--- a/Trắc nghiệm ôn luyện/Embedded Software/multiple_choice_sample_template_EMBEDDED_ARCHITECTURE.xlsx
+++ b/Trắc nghiệm ôn luyện/Embedded Software/multiple_choice_sample_template_EMBEDDED_ARCHITECTURE.xlsx
@@ -453,7 +453,7 @@
         <v>Super Loop (Bare-metal) là kiến trúc cơ bản nhất của lập trình nhúng: `main()` -&gt; Khởi tạo ngoại vi -&gt; `while(1) { task1(); task2(); }`. Chương trình chạy tuần tự từ trên xuống dưới không có hệ điều hành.</v>
       </c>
       <c r="E2" t="str">
-        <v>Cấu trúc chương trình đơn giản gồm hàm khởi tạo chạy một lần và một vòng lặp vô hạn `while(1)` thực thi tuần tự các tác vụ — cấu trúc tuần tự while(1)</v>
+        <v>Cơ chế tự động reset lại chip khi nhiệt độ môi trường tăng lên quá cao — reset nhiệt độ</v>
       </c>
       <c r="F2" t="str">
         <v>Một đoạn mã nguồn code lập trình bị lỗi lặp vô hạn làm sập máy chủ nạp chương trình — lỗi lặp mã nguồn</v>
@@ -462,10 +462,10 @@
         <v>Vòng dây bus vật lý nối các vi điều khiển lại với nhau để truyền dữ liệu chéo — vòng dây bus vật lý</v>
       </c>
       <c r="H2" t="str">
-        <v>Cơ chế tự động reset lại chip khi nhiệt độ môi trường tăng lên quá cao — reset nhiệt độ</v>
+        <v>Cấu trúc chương trình đơn giản gồm hàm khởi tạo chạy một lần và một vòng lặp vô hạn `while(1)` thực thi tuần tự các tác vụ — cấu trúc tuần tự while(1)</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Phân tầng giúp code nhúng độc lập với phần cứng. Ví dụ: Tầng Application gọi hàm `Led_On()`. Hàm này gọi tầng HAL `HAL_GPIO_WritePin()`. Khi đổi sang chip khác, ta chỉ cần viết lại tầng HAL mà không cần sửa code xử lý logic ở tầng Application.</v>
       </c>
       <c r="E3" t="str">
-        <v>Application Layer (Ứng dụng), Middleware/Driver Layer (Trình điều khiển), HAL (Phần cứng trừu tượng) — kiến trúc phân tầng chuẩn nhúng</v>
+        <v>UI Layer, Controller Layer, Network Layer — kiến trúc ứng dụng di động</v>
       </c>
       <c r="F3" t="str">
         <v>Frontend Layer, Backend Layer, Database Layer — kiến trúc phân tầng web chuẩn</v>
       </c>
       <c r="G3" t="str">
-        <v>UI Layer, Controller Layer, Network Layer — kiến trúc ứng dụng di động</v>
+        <v>Application Layer (Ứng dụng), Middleware/Driver Layer (Trình điều khiển), HAL (Phần cứng trừu tượng) — kiến trúc phân tầng chuẩn nhúng</v>
       </c>
       <c r="H3" t="str">
         <v>Security Layer, Compiler Layer, Operating System Layer — kiến trúc bảo mật máy tính</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>FSM giúp thiết kế code điều khiển cực kỳ rõ ràng, tránh việc viết quá nhiều câu lệnh lồng nhau `if-else` phức tạp. Thường được triển khai bằng từ khóa `switch-case` kết hợp với `enum` trạng thái.</v>
       </c>
       <c r="E4" t="str">
+        <v>Tính toán chính xác số lượng bóng bán dẫn được tích hợp trong con chip vi điều khiển — cấu trúc transistor</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Tự động tối ưu hóa dung lượng của file chạy binary sau khi biên dịch xong — tối ưu dung lượng tệp nạp</v>
+      </c>
+      <c r="G4" t="str">
         <v>Quản lý các trạng thái hoạt động của hệ thống (ví dụ: Stop, Run, Error) và các điều kiện chuyển trạng thái rõ ràng — quản lý trạng thái hệ thống</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Tính toán chính xác số lượng bóng bán dẫn được tích hợp trong con chip vi điều khiển — cấu trúc transistor</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Tự động tối ưu hóa dung lượng của file chạy binary sau khi biên dịch xong — tối ưu dung lượng tệp nạp</v>
       </c>
       <c r="H4" t="str">
         <v>Đo lường điện áp tiêu thụ của toàn bộ bảng mạch điện tử khi chạy tải tối đa — đo điện áp mạch</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Watchdog Timer giống như một quả bom hẹn giờ. Chương trình hoạt động bình thường phải liên tục reset bộ đếm này (gọi là "clear watchdog" hoặc "feed the dog"). Nếu code bị treo ở vòng lặp vô hạn, watchdog không được feed sẽ đếm tràn và kích hoạt ngắt reset lại vi điều khiển.</v>
       </c>
       <c r="E5" t="str">
+        <v>Đo lường thời gian trôi qua và hiển thị giờ, phút, giây lên màn hình led — bộ hiển thị đồng hồ thời gian</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Tự động mã hóa toàn bộ dữ liệu lưu trong bộ nhớ Flash của vi điều khiển — mã hóa dữ liệu Flash</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Kết nối mạng không dây Wi-Fi để truyền dữ liệu về máy chủ giám sát — kết nối Wi-Fi</v>
+      </c>
+      <c r="H5" t="str">
         <v>Giám sát hoạt động của chương trình và tự động reset lại chip nếu hệ thống bị treo hoặc chạy sai luồng — giám sát reset hệ thống khi treo</v>
       </c>
-      <c r="F5" t="str">
-        <v>Đo lường thời gian trôi qua và hiển thị giờ, phút, giây lên màn hình led — bộ hiển thị đồng hồ thời gian</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Tự động mã hóa toàn bộ dữ liệu lưu trong bộ nhớ Flash của vi điều khiển — mã hóa dữ liệu Flash</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Kết nối mạng không dây Wi-Fi để truyền dữ liệu về máy chủ giám sát — kết nối Wi-Fi</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>Bare-metal programming là viết code chạy trực tiếp trên vi điều khiển (thường dùng kiến trúc Super Loop hoặc Interrupt-driven), thích hợp cho các dòng chip nhỏ, yêu cầu tài nguyên RAM/Flash cực thấp.</v>
       </c>
       <c r="E6" t="str">
+        <v>Chỉ viết code bằng ngôn ngữ lập trình Assembly thô sơ nhất — lập trình Assembly thô</v>
+      </c>
+      <c r="F6" t="str">
         <v>Lập trình trực tiếp tương tác với phần cứng vi điều khiển mà không sử dụng bất kỳ hệ điều hành (RTOS) nào — lập trình không hệ điều hành</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>Sử dụng các thanh kim loại vật lý để hàn bảo vệ vỏ ngoài của con chip vi điều khiển — bảo vệ kim loại vỏ chip</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Chỉ viết code bằng ngôn ngữ lập trình Assembly thô sơ nhất — lập trình Assembly thô</v>
       </c>
       <c r="H6" t="str">
         <v>Quá trình tẩy sạch lớp oxit đồng trên bề mặt bảng mạch in PCB trước khi hàn linh kiện — tẩy bảng mạch in PCB</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>HAL (Hardware Abstraction Layer) do nhà sản xuất chip cung cấp (ví dụ: STM32Cube HAL). Nó trừu tượng hóa phần cứng bằng cách cung cấp các hàm như `HAL_GPIO_TogglePin()`, giúp lập trình viên không cần nhớ địa chỉ thanh ghi cụ thể.</v>
       </c>
       <c r="E7" t="str">
+        <v>Tính toán chi phí nguyên vật liệu cần thiết để sản xuất ra bảng mạch điện tử — tính chi phí sản xuất</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Dịch mã nguồn ngôn ngữ C sang mã nguồn ngôn ngữ Python để chạy thử nghiệm — dịch dịch ngôn ngữ code</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Tự động quét và vá các lỗ hổng bảo mật của hệ điều hành thời gian thực — quét lỗ hổng bảo mật</v>
+      </c>
+      <c r="H7" t="str">
         <v>Cung cấp các hàm API chuẩn hóa để tương tác với ngoại vi phần cứng, giúp che giấu cấu trúc thanh ghi phức tạp của chip — trừu tượng hóa phần cứng</v>
       </c>
-      <c r="F7" t="str">
-        <v>Tự động quét và vá các lỗ hổng bảo mật của hệ điều hành thời gian thực — quét lỗ hổng bảo mật</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Tính toán chi phí nguyên vật liệu cần thiết để sản xuất ra bảng mạch điện tử — tính chi phí sản xuất</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Dịch mã nguồn ngôn ngữ C sang mã nguồn ngôn ngữ Python để chạy thử nghiệm — dịch dịch ngôn ngữ code</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -659,13 +659,13 @@
         <v>Hệ thống ở chế độ ngủ (Sleep) rảnh rỗi và chỉ thức dậy xử lý công việc khi có sự kiện ngắt phần cứng xảy ra — xử lý dựa trên sự kiện ngắt</v>
       </c>
       <c r="F9" t="str">
+        <v>Toàn bộ mã nguồn chương trình được thực hiện hoàn toàn song song trên 100 con chip khác nhau — đa xử lý song song</v>
+      </c>
+      <c r="G9" t="str">
         <v>Lập trình viên liên tục gọi lệnh reset chip trong vòng lặp vô hạn while(1) — reset liên tục</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Hệ thống bắt buộc phải gửi dữ liệu lên máy chủ internet cứ sau mỗi 5 giây — truyền dữ liệu định kỳ</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Toàn bộ mã nguồn chương trình được thực hiện hoàn toàn song song trên 100 con chip khác nhau — đa xử lý song song</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -685,19 +685,19 @@
         <v>Trong Super Loop, MCU phải liên tục chạy vòng lặp để kiểm tra xem nút có nhấn không, cảm biến có dữ liệu không (Polling), giữ MCU hoạt động ở tần số cao gây hao pin. Event-driven sử dụng ngắt cạnh (Edge Interrupts) cho phép MCU tắt xung nhịp (Sleep) và chỉ hoạt động khi có xung tín hiệu kích hoạt.</v>
       </c>
       <c r="E10" t="str">
+        <v>Vì Event-Driven tự động sửa các lỗi phần cứng trên bảng mạch khi có chập điện — tự động sửa lỗi phần cứng</v>
+      </c>
+      <c r="F10" t="str">
         <v>Vì Polling liên tục quét ngoại vi làm tiêu tốn năng lượng vô ích; Event-Driven cho phép MCU ngủ sâu (Deep Sleep) và chỉ thức dậy xử lý khi có ngắt sự kiện — tiết kiệm điện năng nhờ chế độ ngủ</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
+        <v>Vì Polling làm tăng kích thước file nhị phân sau khi biên dịch lên gấp 10 lần — tăng dung lượng tệp nạp</v>
+      </c>
+      <c r="H10" t="str">
         <v>Vì Polling chỉ chạy được trên các dòng vi điều khiển ARM Cortex-M4 — giới hạn dòng chip Polling</v>
       </c>
-      <c r="G10" t="str">
-        <v>Vì Event-Driven tự động sửa các lỗi phần cứng trên bảng mạch khi có chập điện — tự động sửa lỗi phần cứng</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Vì Polling làm tăng kích thước file nhị phân sau khi biên dịch lên gấp 10 lần — tăng dung lượng tệp nạp</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -717,10 +717,10 @@
         <v>Để đảm bảo firmware ứng dụng đã được nạp hoàn chỉnh, không bị lỗi truyền dẫn hoặc lỗi hỏng bộ nhớ Flash có thể làm sập chip khi jump — kiểm tra tính toàn vẹn của firmware</v>
       </c>
       <c r="F11" t="str">
+        <v>Để tự động tăng tốc độ xử lý xung nhịp của vi điều khiển lên mức tối đa — tăng tốc độ xung nhịp chip</v>
+      </c>
+      <c r="G11" t="str">
         <v>Để giải nén kích thước file binary ứng dụng từ dạng zip sang dạng hex trên Flash — giải nén tệp tin</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Để tự động tăng tốc độ xử lý xung nhịp của vi điều khiển lên mức tối đa — tăng tốc độ xung nhịp chip</v>
       </c>
       <c r="H11" t="str">
         <v>Để mã hóa bảo mật chống hacker có thể đọc trộm mã nguồn code từ bên ngoài — bảo mật chống đọc trộm</v>
@@ -743,19 +743,19 @@
         <v>Đối với FSM nhỏ, switch-case là đủ tốt. Tuy nhiên, khi FSM có hàng chục trạng thái và điều kiện chuyển phức tạp, switch-case sẽ trở thành thảm họa khó đọc. Sử dụng mảng cấu trúc (struct) chứa: trạng thái hiện tại, sự kiện kích hoạt, trạng thái tiếp theo và con trỏ hàm xử lý (State Transition Table) giúp code sạch sẽ, dễ mở rộng.</v>
       </c>
       <c r="E12" t="str">
-        <v>Sử dụng bảng con trỏ hàm (State Transition Table / Function Pointers) trỏ tới các hàm xử lý trạng thái tương ứng — con trỏ hàm xử lý trạng thái</v>
+        <v>Sử dụng các câu lệnh nhảy không điều kiện `goto` để di chuyển tự do giữa các trạng thái — câu lệnh goto tự do rủi ro</v>
       </c>
       <c r="F12" t="str">
         <v>Viết một câu lệnh switch-case khổng lồ chứa hàng nghìn dòng code lồng nhau — switch-case khổng lồ khó đọc</v>
       </c>
       <c r="G12" t="str">
-        <v>Sử dụng các câu lệnh nhảy không điều kiện `goto` để di chuyển tự do giữa các trạng thái — câu lệnh goto tự do rủi ro</v>
+        <v>Sử dụng bảng con trỏ hàm (State Transition Table / Function Pointers) trỏ tới các hàm xử lý trạng thái tương ứng — con trỏ hàm xử lý trạng thái</v>
       </c>
       <c r="H12" t="str">
         <v>Khai báo tất cả các trạng thái thành các biến toàn cục kiểu số thực float — sử dụng biến float</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -772,19 +772,19 @@
         <v>HAL cung cấp API cho chip (như ADC, SPI, GPIO). BSP được xây dựng trên HAL, cung cấp API cho thiết bị cụ thể gắn trên board (ví dụ: Board STM32 Discovery có cảm biến gia tốc LIS3DSH, BSP cung cấp các hàm như `BSP_ACCELERO_Init()`, giúp ẩn đi việc giao tiếp SPI phức tạp cấu hình cho chip gia tốc đó).</v>
       </c>
       <c r="E13" t="str">
+        <v>HAL chỉ dùng cho lập trình nhúng 8-bit; còn BSP chỉ dùng cho lập trình nhúng 32-bit — phân loại theo bit chip</v>
+      </c>
+      <c r="F13" t="str">
         <v>HAL trừu tượng hóa vi điều khiển (MCU peripherals); BSP trừu tượng hóa toàn bộ bo mạch cụ thể bao gồm cả các linh kiện ngoại vi hàn trên bo mạch đó — trừu tượng hóa MCU vs trừu tượng hóa toàn bo mạch</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>HAL viết bằng ngôn ngữ Assembly; còn BSP viết bằng ngôn ngữ C — ngôn ngữ lập trình viết lớp</v>
-      </c>
-      <c r="G13" t="str">
-        <v>HAL chỉ dùng cho lập trình nhúng 8-bit; còn BSP chỉ dùng cho lập trình nhúng 32-bit — phân loại theo bit chip</v>
       </c>
       <c r="H13" t="str">
         <v>HAL bắt buộc phải mua bản quyền thương mại; còn BSP hoàn toàn miễn phí cho mọi người dùng — chi phí bản quyền</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -801,10 +801,10 @@
         <v>Lệnh feed watchdog (ví dụ `HAL_IWDG_Refresh()`) chỉ nên đặt ở duy nhất một vị trí an toàn (thường là cuối Super Loop sau khi tất cả các task đã hoàn thành bình thường). Nếu đặt rải rác hoặc đặt trong hàm ngắt timer, watchdog vẫn được feed đều đặn ngay cả khi chương trình chính đã bị treo cứng, vô hiệu hóa chức năng bảo vệ của WDT.</v>
       </c>
       <c r="E14" t="str">
+        <v>Vì feed watchdog nhiều nơi sẽ làm sụt áp nguồn điện của vi điều khiển ngay lập tức — sụt áp nguồn điện chip</v>
+      </c>
+      <c r="F14" t="str">
         <v>Vì nếu một đoạn code bị treo ở vòng lặp vô hạn nhưng trong vòng lặp đó vẫn có lệnh feed watchdog, hệ thống sẽ không bao giờ được reset mặc dù đã bị treo — feed watchdog trong vòng lặp treo làm mất tác dụng WDT</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Vì feed watchdog nhiều nơi sẽ làm sụt áp nguồn điện của vi điều khiển ngay lập tức — sụt áp nguồn điện chip</v>
       </c>
       <c r="G14" t="str">
         <v>Vì WDT chỉ cho phép gọi lệnh feed đúng 1 lần duy nhất trong suốt vòng đời của chip — giới hạn số lần gọi</v>
@@ -813,7 +813,7 @@
         <v>Vì nó làm cho vi điều khiển hoạt động nóng hơn gấp đôi so với bình thường — tăng sinh nhiệt phần cứng</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>FOTA an toàn đòi hỏi cơ chế Dual-bank (hoặc phân vùng Application Active và Application Download). Khi tải OTA, firmware mới được ghi vào Bank 1. Khi tải xong và validate CRC thành công, Bootloader mới đổi cờ khởi động sang Bank 1. Nếu đang tải mà mất điện, hệ thống vẫn khởi động an toàn từ Bank 0 cũ, tránh rủi ro biến thiết bị thành "cục gạch" (bricking).</v>
       </c>
       <c r="E15" t="str">
-        <v>Phải có cơ chế phân vùng bộ nhớ Dual-bank Flash (gồm Bank 0 chứa Application đang chạy, Bank 1 chứa ứng dụng mới đang tải về) để rollback nếu cập nhật thất bại — phân vùng Dual-bank Flash</v>
+        <v>Phải hỗ trợ kết nối trực tiếp với thẻ nhớ ngoài SD chạy song song — thẻ nhớ ngoài SD</v>
       </c>
       <c r="F15" t="str">
         <v>Phải có dung lượng Flash tối thiểu từ 16GB trở lên giống như trên điện thoại di động di động — yêu cầu dung lượng Flash lớn</v>
       </c>
       <c r="G15" t="str">
-        <v>Phải hỗ trợ kết nối trực tiếp với thẻ nhớ ngoài SD chạy song song — thẻ nhớ ngoài SD</v>
+        <v>Phải có cơ chế phân vùng bộ nhớ Dual-bank Flash (gồm Bank 0 chứa Application đang chạy, Bank 1 chứa ứng dụng mới đang tải về) để rollback nếu cập nhật thất bại — phân vùng Dual-bank Flash</v>
       </c>
       <c r="H15" t="str">
         <v>Chỉ được phép sử dụng bộ nhớ RAM để lưu trữ firmware mới chứ không nạp vào Flash — nạp vào RAM</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>Callback đăng ký con trỏ hàm. Ví dụ: khi nhận xong 1 byte UART, HAL phát sinh ngắt và tự động gọi hàm callback `HAL_UART_RxCpltCallback()`. Lập trình viên chỉ cần viết logic xử lý byte đó trong hàm callback ở lớp Application mà không cần sửa code Driver của HAL.</v>
       </c>
       <c r="E16" t="str">
-        <v>Cho phép lớp phần cứng (driver/HAL) kích hoạt ngược lại một hàm xử lý được định nghĩa ở lớp ứng dụng (application) khi có sự kiện ngắt xảy ra — gọi ngược hàm xử lý lớp ứng dụng</v>
+        <v>Mã hóa toàn bộ các bản tin dữ liệu truyền đi qua giao thức UART sang mã Hex — mã hóa dữ liệu UART</v>
       </c>
       <c r="F16" t="str">
         <v>Tự động xóa các biến toàn cục không sử dụng ra khỏi bộ nhớ của vi điều khiển — tự động xóa biến rác</v>
       </c>
       <c r="G16" t="str">
-        <v>Mã hóa toàn bộ các bản tin dữ liệu truyền đi qua giao thức UART sang mã Hex — mã hóa dữ liệu UART</v>
+        <v>Yêu cầu lập trình viên phải chạy chương trình mô phỏng trên phần mềm trước khi nạp vào chip — mô phỏng bắt buộc</v>
       </c>
       <c r="H16" t="str">
-        <v>Yêu cầu lập trình viên phải chạy chương trình mô phỏng trên phần mềm trước khi nạp vào chip — mô phỏng bắt buộc</v>
+        <v>Cho phép lớp phần cứng (driver/HAL) kích hoạt ngược lại một hàm xử lý được định nghĩa ở lớp ứng dụng (application) khi có sự kiện ngắt xảy ra — gọi ngược hàm xử lý lớp ứng dụng</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Trình biên dịch khi tối ưu hóa (Optimization levels -O2, -O3) thấy biến toàn cục không bị sửa đổi trong vòng lặp `while(1)` chính sẽ cất nó vào thanh ghi CPU để đọc nhanh. Nhưng ISR có thể sửa biến này dưới phần cứng. Nếu thiếu `volatile`, vòng lặp chính sẽ đọc giá trị cũ trong thanh ghi mãi mãi, gây lỗi logic hệ thống.</v>
       </c>
       <c r="E17" t="str">
+        <v>Để hệ thống tự động khóa tất cả các ngắt chéo khi biến này đang được ghi dữ liệu — tự động khóa ngắt chéo</v>
+      </c>
+      <c r="F17" t="str">
         <v>Để báo cho trình biên dịch (Compiler) không được tối ưu hóa biến này vào thanh ghi, bắt buộc phải đọc trực tiếp từ bộ nhớ RAM vì giá trị có thể thay đổi bất ngờ ngoài luồng chính — ngăn chặn tối ưu hóa trình biên dịch</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>Để tăng tốc độ đọc ghi của biến này trên bộ nhớ RAM lên nhanh gấp 10 lần — tăng tốc độ đọc ghi biến</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Để hệ thống tự động khóa tất cả các ngắt chéo khi biến này đang được ghi dữ liệu — tự động khóa ngắt chéo</v>
       </c>
       <c r="H17" t="str">
         <v>Vì nếu không có volatile, vi điều khiển sẽ tự động reset lại chip khi biến đó nhận giá trị số âm — reset khi giá trị âm</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -920,10 +920,10 @@
         <v>Vì malloc tốn tài nguyên quản lý của heap, có rủi ro rò rỉ bộ nhớ (memory leak) và gây phân mảnh RAM dẫn đến việc không thể cấp phát được sau một thời gian chạy — rủi ro phân mảnh và cạn kiệt RAM</v>
       </c>
       <c r="F18" t="str">
+        <v>Vì hàm free() tự động xóa bỏ toàn bộ mã nguồn chương trình lưu trong Flash của chip — tự động xóa code</v>
+      </c>
+      <c r="G18" t="str">
         <v>Vì malloc chỉ hoạt động được trên các vi điều khiển hỗ trợ hệ điều hành RTOS — giới hạn hệ điều hành</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Vì hàm free() tự động xóa bỏ toàn bộ mã nguồn chương trình lưu trong Flash của chip — tự động xóa code</v>
       </c>
       <c r="H18" t="str">
         <v>Vì cấp phát động bắt buộc vi điều khiển phải chạy ở tần số xung nhịp tối thiểu là 100MHz — giới hạn tần số chip</v>
@@ -949,13 +949,13 @@
         <v>Thiết kế kiến trúc hướng sự kiện (Event-driven): Sử dụng ngắt DMA để nhận/gửi dữ liệu UART và SPI vào các bộ đệm vòng (Ring Buffers); xử lý ghi Flash và truyền 4G ở luồng chính (background task) để không chặn việc lấy mẫu cảm biến — DMA Ring Buffers kết hợp xử lý tầng nền</v>
       </c>
       <c r="F19" t="str">
-        <v>Sử dụng kiến trúc Super Loop (Bare-metal) chạy tuần tự: Đọc cảm biến -&gt; Ghi Flash -&gt; Gửi 4G UART; dùng hàm delay_ms() để chờ phản hồi từ modem 4G — Super Loop tuần tự rủi ro mất mát dữ liệu</v>
+        <v>Thiết kế để cảm biến SPI tự động gửi dữ liệu trực tiếp vào modem 4G UART mà không đi qua vi điều khiển trung gian — truyền trực tiếp ngoại vi không hỗ trợ</v>
       </c>
       <c r="G19" t="str">
         <v>Sử dụng hệ điều hành RTOS và đưa tất cả các tác vụ đọc cảm biến, ghi Flash và truyền 4G vào chung một Task có độ ưu tiên cao nhất — chung một task không tối ưu đa nhiệm</v>
       </c>
       <c r="H19" t="str">
-        <v>Thiết kế để cảm biến SPI tự động gửi dữ liệu trực tiếp vào modem 4G UART mà không đi qua vi điều khiển trung gian — truyền trực tiếp ngoại vi không hỗ trợ</v>
+        <v>Sử dụng kiến trúc Super Loop (Bare-metal) chạy tuần tự: Đọc cảm biến -&gt; Ghi Flash -&gt; Gửi 4G UART; dùng hàm delay_ms() để chờ phản hồi từ modem 4G — Super Loop tuần tự rủi ro mất mát dữ liệu</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -975,19 +975,19 @@
         <v>Nếu không tắt các ngắt ngoại vi và SysTick của Bootloader trước khi Jump, khi sang chương trình Application, một ngắt cũ xảy ra sẽ nhảy vào địa chỉ xử lý ngắt (ISR vector table) của Bootloader cũ, gây lỗi nhảy vùng nhớ bậy (HardFault). Cấu hình lại MSP (Main Stack Pointer) về địa chỉ đỉnh stack của ứng dụng mới là bắt buộc để ứng dụng chạy đúng vùng nhớ RAM cấp phát của nó.</v>
       </c>
       <c r="E20" t="str">
+        <v>Chỉ cần gọi trực tiếp con trỏ hàm trỏ đến địa chỉ Flash của ứng dụng mới mà không cần tắt ngắt hay cấu hình lại MSP — jump trực tiếp rủi ro sập ngắt</v>
+      </c>
+      <c r="F20" t="str">
         <v>Tắt toàn bộ các ngắt ngoại vi, reset lại cấu hình NVIC, tắt ngắt hệ thống SysTick, thiết lập con trỏ Stack Pointer (MSP) về địa chỉ bắt đầu của ứng dụng mới, và gọi con trỏ hàm trỏ đến Vector Reset của ứng dụng mới — de-initialize ngoại vi cấu hình Stack Pointer và jump Vector Reset</v>
       </c>
-      <c r="F20" t="str">
-        <v>Chỉ cần gọi trực tiếp con trỏ hàm trỏ đến địa chỉ Flash của ứng dụng mới mà không cần tắt ngắt hay cấu hình lại MSP — jump trực tiếp rủi ro sập ngắt</v>
-      </c>
       <c r="G20" t="str">
+        <v>Gửi một bản tin UART báo cáo trạng thái thành công về máy tính và tắt nguồn điện của chip — tắt nguồn chip</v>
+      </c>
+      <c r="H20" t="str">
         <v>Thực hiện xóa bỏ phân vùng bộ nhớ của Bootloader trên Flash để nhường chỗ cho ứng dụng mới chạy — xóa bộ nhớ Bootloader nguy hiểm</v>
       </c>
-      <c r="H20" t="str">
-        <v>Gửi một bản tin UART báo cáo trạng thái thành công về máy tính và tắt nguồn điện của chip — tắt nguồn chip</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1007,13 +1007,13 @@
         <v>Harvard có đường bus độc lập cho bộ nhớ chương trình (Code) và bộ nhớ dữ liệu (Data), cho phép CPU đọc lệnh và truy xuất dữ liệu song song; Von Neumann sử dụng chung một đường bus chung cho cả hai, gây nghẽn cổ chai bus (bus bottleneck) — bus độc lập song song vs bus dùng chung nghẽn cổ chai</v>
       </c>
       <c r="F21" t="str">
+        <v>Harvard bắt buộc sử dụng bộ nhớ ngoài Flash dạng thẻ nhớ SD; còn Von Neumann chỉ hỗ trợ RAM tĩnh SRAM — phân loại công nghệ bộ nhớ</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Harvard tiêu thụ điện năng nhiều gấp 10 lần so với Von Neumann do kiến trúc bus phức tạp — so sánh tiêu thụ điện năng</v>
+      </c>
+      <c r="H21" t="str">
         <v>Harvard chỉ chạy được trên các dòng vi điều khiển 8-bit; còn Von Neumann chỉ chạy trên các dòng vi xử lý 64-bit — phân loại theo số bit</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Harvard bắt buộc sử dụng bộ nhớ ngoài Flash dạng thẻ nhớ SD; còn Von Neumann chỉ hỗ trợ RAM tĩnh SRAM — phân loại công nghệ bộ nhớ</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Harvard tiêu thụ điện năng nhiều gấp 10 lần so với Von Neumann do kiến trúc bus phức tạp — so sánh tiêu thụ điện năng</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         <v>HSM cho phép các trạng thái con kế thừa các hành vi chuyển trạng thái (Transitions) của trạng thái cha, giúp nhóm các logic xử lý chung và giảm thiểu số lượng đường nối chuyển trạng thái chéo chằng chịt — kế thừa trạng thái giảm bùng nổ trạng thái</v>
       </c>
       <c r="F22" t="str">
-        <v>HSM sử dụng trí tuệ nhân tạo AI để tự động dự báo các trạng thái tiếp theo của hệ thống — tự động dự báo trạng thái</v>
+        <v>HSM tự động xóa bỏ hoàn toàn các trạng thái lỗi hệ thống để đơn giản hóa sơ đồ — xóa bỏ trạng thái lỗi</v>
       </c>
       <c r="G22" t="str">
         <v>HSM bắt buộc toàn bộ dữ liệu trạng thái phải được lưu trên một máy chủ cơ sở dữ liệu bên ngoài chip — lưu trữ cơ sở dữ liệu ngoài</v>
       </c>
       <c r="H22" t="str">
-        <v>HSM tự động xóa bỏ hoàn toàn các trạng thái lỗi hệ thống để đơn giản hóa sơ đồ — xóa bỏ trạng thái lỗi</v>
+        <v>HSM sử dụng trí tuệ nhân tạo AI để tự động dự báo các trạng thái tiếp theo của hệ thống — tự động dự báo trạng thái</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1062,19 +1062,19 @@
         <v>Lỗi lớn nhất của người mới học là viết code quá nặng (như `printf`, ghi Flash, delay) trong ISR. Vì khi ISR đang chạy, các ngắt có độ ưu tiên thấp hơn sẽ bị chặn hoàn toàn, gây mất mát dữ liệu ngoại vi khác và tăng vọt độ trễ ngắt toàn hệ thống. Quy tắc vàng: ISR là người phát tin báo (nhanh nhất có thể), chương trình chính là người xử lý tin.</v>
       </c>
       <c r="E23" t="str">
-        <v>Giữ cho các chương trình phục vụ ngắt (ISR) cực kỳ ngắn gọn (chỉ xóa cờ ngắt, đọc dữ liệu thô và đẩy vào buffer/queue), tuyệt đối không gọi các hàm block/delay, không gọi API IO nặng; xử lý logic chạy ở ngoài ISR — tối giản hóa ISR xử lý logic ở background</v>
+        <v>Yêu cầu vi điều khiển phải chạy ở chế độ xung nhịp thấp nhất để giảm thiểu nhiễu tín hiệu ngắt — giảm xung nhịp chip</v>
       </c>
       <c r="F23" t="str">
         <v>Đưa toàn bộ thuật toán điều khiển phanh phức tạp và việc gửi dữ liệu hiển thị LCD vào chạy trực tiếp trong ISR của ngắt — chạy thuật toán nặng trong ISR</v>
       </c>
       <c r="G23" t="str">
+        <v>Giữ cho các chương trình phục vụ ngắt (ISR) cực kỳ ngắn gọn (chỉ xóa cờ ngắt, đọc dữ liệu thô và đẩy vào buffer/queue), tuyệt đối không gọi các hàm block/delay, không gọi API IO nặng; xử lý logic chạy ở ngoài ISR — tối giản hóa ISR xử lý logic ở background</v>
+      </c>
+      <c r="H23" t="str">
         <v>Tắt toàn bộ các ngắt của vi điều khiển và chuyển sang sử dụng cơ chế Polling quét tuần tự trong Super Loop — tắt ngắt chuyển Polling</v>
       </c>
-      <c r="H23" t="str">
-        <v>Yêu cầu vi điều khiển phải chạy ở chế độ xung nhịp thấp nhất để giảm thiểu nhiễu tín hiệu ngắt — giảm xung nhịp chip</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Trong AUTOSAR, RTE là lớp cốt lõi. Nó che giấu việc triển khai thực tế của các liên kết. Một Component A gửi dữ liệu cho Component B thông qua các cổng RTE (RTE ports). Việc 2 component này nằm trên cùng 1 chip hay nằm ở 2 ECU khác nhau giao tiếp qua mạng CAN hoàn toàn do RTE xử lý cấu hình, giúp tăng khả năng tái sử dụng phần mềm xe hơi cực cao.</v>
       </c>
       <c r="E24" t="str">
+        <v>Là hệ thống điều hòa tự động điều chỉnh nhiệt độ cho con chip vi điều khiển trên mạch — điều hòa nhiệt độ chip</v>
+      </c>
+      <c r="F24" t="str">
         <v>Đóng vai trò là cầu nối giao tiếp trung gian (trừu tượng hóa hoàn toàn) giữa các thành phần ứng dụng phần mềm (Software Components - SWCs) với nhau và giữa SWCs với tầng dịch vụ phần mềm cơ sở (BSW) — trừu tượng hóa giao tiếp ứng dụng và bsw</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>Đóng vai trò tự động nạp lại chương trình ứng dụng mới cho hộp ECU thông qua cổng giao tiếp OBD-II — nạp chương trình tự động</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v>Chịu trách nhiệm mã hóa toàn bộ dữ liệu truyền thông trên mạng CAN bus của xe ô tô — mã hóa CAN bus</v>
       </c>
-      <c r="H24" t="str">
-        <v>Là hệ thống điều hòa tự động điều chỉnh nhiệt độ cho con chip vi điều khiển trên mạch — điều hòa nhiệt độ chip</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Cảm biến gia tốc đo trọng lực rất tốt ở trạng thái tĩnh nhưng bị nhiễu cực mạnh khi drone rung động do động cơ quay. Cảm biến con quay đo tốc độ góc rất nhanh nhưng khi tích phân tính góc sẽ bị lỗi tích lũy (drift) làm sai góc sau vài phút. Lọc Kalman/Bù kết hợp điểm mạnh của cả hai cảm biến để ước lượng góc nghiêng chính xác, giúp drone giữ thăng bằng ổn định.</v>
       </c>
       <c r="E25" t="str">
-        <v>Để kết hợp và lọc nhiễu tín hiệu từ cảm biến gia tốc (Accelerometer - nhạy với nhiễu động) và cảm biến con quay hồi chuyển (Gyroscope - bị trôi góc theo thời gian) nhằm tính toán chính xác góc nghiêng của drone — lọc kết hợp cảm biến IMU</v>
+        <v>Để đảm bảo pin của thiết bị drone tự động sạc đầy trong vòng 5 phút khi đang bay — sạc pin drone</v>
       </c>
       <c r="F25" t="str">
         <v>Để tự động điều chỉnh tốc độ quay của quạt tản nhiệt máy bay theo nhiệt độ môi trường — tản nhiệt drone</v>
       </c>
       <c r="G25" t="str">
+        <v>Để kết hợp và lọc nhiễu tín hiệu từ cảm biến gia tốc (Accelerometer - nhạy với nhiễu động) và cảm biến con quay hồi chuyển (Gyroscope - bị trôi góc theo thời gian) nhằm tính toán chính xác góc nghiêng của drone — lọc kết hợp cảm biến IMU</v>
+      </c>
+      <c r="H25" t="str">
         <v>Để mã hóa toàn bộ hình ảnh camera gửi từ máy bay về điện thoại của người điều khiển — mã hóa hình ảnh camera</v>
       </c>
-      <c r="H25" t="str">
-        <v>Để đảm bảo pin của thiết bị drone tự động sạc đầy trong vòng 5 phút khi đang bay — sạc pin drone</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
         <v>ARM TrustZone mang lại bảo mật ở tầng phần cứng (hardware-enforced isolation). Ngay cả khi hacker khai thác thành công lỗi tràn bộ đệm ở tầng ứng dụng (Non-secure World) để chiếm quyền root, hacker vẫn không thể truy cập vào vùng nhớ RAM, thanh ghi ngoại vi hoặc bộ nhớ Flash thuộc phân vùng Secure World, bảo vệ an toàn cho các dữ liệu nhạy cảm.</v>
       </c>
       <c r="E26" t="str">
-        <v>Nó chia tách bộ xử lý vật lý thành hai phân vùng ảo độc lập: Phân vùng bảo mật (Secure World) chứa key, mật mã, bootloader an toàn và Phân vùng thông thường (Non-secure World) chạy OS/Application — ARM TrustZone phân vùng bảo mật phần cứng</v>
+        <v>Nó bắt buộc toàn bộ mã nguồn chương trình phải được lưu trên máy chủ Cloud của ARM — lưu trữ đám mây ARM</v>
       </c>
       <c r="F26" t="str">
         <v>Nó tự động ngắt kết nối nguồn điện của chip nếu phát hiện có thiết bị ngoại vi lạ cắm vào — ngắt nguồn chip</v>
@@ -1158,10 +1158,10 @@
         <v>Nó yêu cầu lập trình viên phải quét dấu vân tay mỗi khi muốn nạp code mới vào chip — quét vân tay nạp code</v>
       </c>
       <c r="H26" t="str">
-        <v>Nó bắt buộc toàn bộ mã nguồn chương trình phải được lưu trên máy chủ Cloud của ARM — lưu trữ đám mây ARM</v>
+        <v>Nó chia tách bộ xử lý vật lý thành hai phân vùng ảo độc lập: Phân vùng bảo mật (Secure World) chứa key, mật mã, bootloader an toàn và Phân vùng thông thường (Non-secure World) chạy OS/Application — ARM TrustZone phân vùng bảo mật phần cứng</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
